--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\OneDrive\Bureau\isamm-student-managment-platform\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB008317-9F33-4586-80FA-2C9C2BF33A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA1EA97-40B8-44CF-9D54-20D08534F9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="-14520" windowWidth="25350" windowHeight="13140" xr2:uid="{AFD31129-8B99-4084-8265-242CB6D304A0}"/>
+    <workbookView xWindow="5625" yWindow="2745" windowWidth="19695" windowHeight="11505" xr2:uid="{AFD31129-8B99-4084-8265-242CB6D304A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>firstName</t>
   </si>
@@ -56,9 +56,6 @@
     <t>phone</t>
   </si>
   <si>
-    <t xml:space="preserve">password </t>
-  </si>
-  <si>
     <t>cv</t>
   </si>
   <si>
@@ -98,48 +95,6 @@
     <t>Ilyes</t>
   </si>
   <si>
-    <t>Aziz</t>
-  </si>
-  <si>
-    <t>Ammar</t>
-  </si>
-  <si>
-    <t>Ines</t>
-  </si>
-  <si>
-    <t>Roua</t>
-  </si>
-  <si>
-    <t>Siwar</t>
-  </si>
-  <si>
-    <t>Nesrine</t>
-  </si>
-  <si>
-    <t>Emna</t>
-  </si>
-  <si>
-    <t>Masmoudi</t>
-  </si>
-  <si>
-    <t>Rezgui</t>
-  </si>
-  <si>
-    <t>Gharbi</t>
-  </si>
-  <si>
-    <t>Amdouni</t>
-  </si>
-  <si>
-    <t>Arafa</t>
-  </si>
-  <si>
-    <t>jmal</t>
-  </si>
-  <si>
-    <t>lahmer</t>
-  </si>
-  <si>
     <t>hafsi</t>
   </si>
   <si>
@@ -164,54 +119,6 @@
     <t>ben Ali</t>
   </si>
   <si>
-    <t>ali123</t>
-  </si>
-  <si>
-    <t>ahmed123</t>
-  </si>
-  <si>
-    <t>amine123</t>
-  </si>
-  <si>
-    <t>amira123</t>
-  </si>
-  <si>
-    <t>islem123</t>
-  </si>
-  <si>
-    <t>ghazi123</t>
-  </si>
-  <si>
-    <t>chiraz123</t>
-  </si>
-  <si>
-    <t>oumaima123</t>
-  </si>
-  <si>
-    <t>ilyes123</t>
-  </si>
-  <si>
-    <t>aziz123</t>
-  </si>
-  <si>
-    <t>ammar123</t>
-  </si>
-  <si>
-    <t>ines123</t>
-  </si>
-  <si>
-    <t>roua123</t>
-  </si>
-  <si>
-    <t>siwar123</t>
-  </si>
-  <si>
-    <t>nesrine123</t>
-  </si>
-  <si>
-    <t>emna123</t>
-  </si>
-  <si>
     <t>ahmed_cv.pdf</t>
   </si>
   <si>
@@ -239,27 +146,6 @@
     <t>ilyes_cv.pdf</t>
   </si>
   <si>
-    <t>aziz_cv.pdf</t>
-  </si>
-  <si>
-    <t>ammar_cv.pdf</t>
-  </si>
-  <si>
-    <t>ines_cv.pdf</t>
-  </si>
-  <si>
-    <t>roua_cv.pdf</t>
-  </si>
-  <si>
-    <t>siwar_cv.pdf</t>
-  </si>
-  <si>
-    <t>nesrine_cv.pdf</t>
-  </si>
-  <si>
-    <t>emna_cv.pdf</t>
-  </si>
-  <si>
     <t>IM</t>
   </si>
   <si>
@@ -272,9 +158,6 @@
     <t>active_student</t>
   </si>
   <si>
-    <t>ahmedbenali@gmail.com</t>
-  </si>
-  <si>
     <t>alimeknimekni@gmail.com</t>
   </si>
   <si>
@@ -299,32 +182,14 @@
     <t>ilyeshafsihafsi@gmail.com</t>
   </si>
   <si>
-    <t>azizlahmerlahmer@gmail.com</t>
-  </si>
-  <si>
-    <t>ammarjmaljmal@gmail.com</t>
-  </si>
-  <si>
-    <t>inesArafaarafa@gmail.com</t>
-  </si>
-  <si>
-    <t>rouaAmdouniamdouni@gmail.com</t>
-  </si>
-  <si>
-    <t>siwarGharbigharbi@gmail.com</t>
-  </si>
-  <si>
-    <t>nesrineRezguirezgui@gmail.com</t>
-  </si>
-  <si>
-    <t>emnaMasmoudimasmoudi@gmail.com</t>
+    <t>ahmedgafsi88@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,6 +208,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -374,12 +247,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -722,7 +595,7 @@
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
@@ -732,7 +605,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -747,11 +620,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -762,569 +635,323 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>19526369</v>
-      </c>
-      <c r="B2" s="3">
+        <v>11526369</v>
+      </c>
+      <c r="B2" s="2">
         <v>36902</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2">
+        <v>26</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2">
         <v>25234567</v>
       </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
       <c r="H2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2">
+        <v>36</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
-      <c r="K2" t="s">
-        <v>77</v>
+      <c r="J2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>19526379</v>
-      </c>
-      <c r="B3" s="3">
+        <v>11526379</v>
+      </c>
+      <c r="B3" s="2">
         <v>36903</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3">
+      <c r="F3">
         <v>25234568</v>
       </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
       <c r="H3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3">
+        <v>36</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="K3" t="s">
-        <v>77</v>
+      <c r="J3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>19526389</v>
-      </c>
-      <c r="B4" s="3">
+        <v>11526389</v>
+      </c>
+      <c r="B4" s="2">
         <v>36904</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4">
+        <v>25234579</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>39</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4">
-        <v>25234579</v>
-      </c>
-      <c r="H4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>19526399</v>
-      </c>
-      <c r="B5" s="3">
+        <v>11526399</v>
+      </c>
+      <c r="B5" s="2">
         <v>36905</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5">
         <v>25234581</v>
       </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
       <c r="H5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5">
+        <v>37</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
-        <v>77</v>
+      <c r="J5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>19526319</v>
-      </c>
-      <c r="B6" s="3">
+        <v>11526319</v>
+      </c>
+      <c r="B6" s="2">
         <v>36906</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6">
+        <v>25234582</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6">
-        <v>25234582</v>
-      </c>
-      <c r="H6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" t="s">
-        <v>76</v>
-      </c>
-      <c r="J6">
+      <c r="I6">
         <v>2</v>
       </c>
-      <c r="K6" t="s">
-        <v>77</v>
+      <c r="J6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>19526329</v>
-      </c>
-      <c r="B7" s="3">
+        <v>11526329</v>
+      </c>
+      <c r="B7" s="2">
         <v>36907</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7">
         <v>25234583</v>
       </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
       <c r="H7" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J7">
+        <v>38</v>
+      </c>
+      <c r="I7">
         <v>2</v>
       </c>
-      <c r="K7" t="s">
-        <v>77</v>
+      <c r="J7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>19526339</v>
-      </c>
-      <c r="B8" s="3">
+        <v>11526339</v>
+      </c>
+      <c r="B8" s="2">
         <v>36908</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>25234584</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8">
-        <v>25234584</v>
-      </c>
-      <c r="H8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8">
+      <c r="I8">
         <v>3</v>
       </c>
-      <c r="K8" t="s">
-        <v>77</v>
+      <c r="J8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>19526349</v>
-      </c>
-      <c r="B9" s="3">
+        <v>11526349</v>
+      </c>
+      <c r="B9" s="2">
         <v>36909</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9">
         <v>25234585</v>
       </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
       <c r="H9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9">
+        <v>36</v>
+      </c>
+      <c r="I9">
         <v>3</v>
       </c>
-      <c r="K9" t="s">
-        <v>77</v>
+      <c r="J9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>19526359</v>
-      </c>
-      <c r="B10" s="3">
+        <v>11526359</v>
+      </c>
+      <c r="B10" s="2">
         <v>36910</v>
       </c>
       <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
+      <c r="E10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10">
         <v>25234586</v>
       </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
       <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10">
+        <v>36</v>
+      </c>
+      <c r="I10">
         <v>3</v>
       </c>
-      <c r="K10" t="s">
-        <v>77</v>
+      <c r="J10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>19526368</v>
-      </c>
-      <c r="B11" s="3">
-        <v>36911</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
-        <v>25234587</v>
-      </c>
-      <c r="H11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11" t="s">
-        <v>77</v>
-      </c>
+      <c r="B11" s="2"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>19526378</v>
-      </c>
-      <c r="B12" s="3">
-        <v>36912</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12">
-        <v>25234588</v>
-      </c>
-      <c r="H12" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12" t="s">
-        <v>77</v>
-      </c>
+      <c r="B12" s="2"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>19526358</v>
-      </c>
-      <c r="B13" s="3">
-        <v>36913</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>25234589</v>
-      </c>
-      <c r="H13" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" t="s">
-        <v>75</v>
-      </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-      <c r="K13" t="s">
-        <v>77</v>
-      </c>
+      <c r="B13" s="2"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>19526348</v>
-      </c>
-      <c r="B14" s="3">
-        <v>36914</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>25234589</v>
-      </c>
-      <c r="H14" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>77</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>19526338</v>
-      </c>
-      <c r="B15" s="3">
-        <v>36915</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
-        <v>25234589</v>
-      </c>
-      <c r="H15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="s">
-        <v>77</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>19526328</v>
-      </c>
-      <c r="B16" s="3">
-        <v>36916</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
-        <v>25234589</v>
-      </c>
-      <c r="H16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>19526318</v>
-      </c>
-      <c r="B17" s="3">
-        <v>36917</v>
-      </c>
-      <c r="C17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>25234589</v>
-      </c>
-      <c r="H17" t="s">
-        <v>73</v>
-      </c>
-      <c r="I17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
-        <v>77</v>
-      </c>
+      <c r="B16" s="2"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="E17" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1337,15 +964,8 @@
     <hyperlink ref="E8" r:id="rId7" xr:uid="{A5057ADE-532C-464A-8B41-755A876B4057}"/>
     <hyperlink ref="E9" r:id="rId8" xr:uid="{C76FA67C-0334-4551-B9D8-273D708CFC3B}"/>
     <hyperlink ref="E10" r:id="rId9" xr:uid="{E0FC9139-189A-467A-A089-323F4CC67101}"/>
-    <hyperlink ref="E11" r:id="rId10" xr:uid="{D687A15C-110E-4D0B-B8FB-34A4D3EBB1D0}"/>
-    <hyperlink ref="E12" r:id="rId11" xr:uid="{CC3CE0D6-E52C-48C3-BE8D-BB5731B078CC}"/>
-    <hyperlink ref="E13" r:id="rId12" xr:uid="{A0C4D5ED-D706-4C23-B6CF-892265709183}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{0379602B-0870-4B4F-88E5-3ED34E045EAF}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{999ED984-7DF8-4E2E-8B98-E07177E32DE2}"/>
-    <hyperlink ref="E16" r:id="rId15" xr:uid="{FF7157FC-4837-48D8-934B-458B9190A73C}"/>
-    <hyperlink ref="E17" r:id="rId16" xr:uid="{2D391ADB-B698-473C-8116-C04B086416D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\OneDrive\Bureau\isamm-student-managment-platform\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\OneDrive\Bureau\Projects\isamm-student-managment-platform\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47994D9-B6B7-48A0-8B05-34DDE6DDB400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DFCFCC-7231-40B0-AB5E-E31B76A902CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5625" yWindow="2745" windowWidth="19695" windowHeight="11505" xr2:uid="{AFD31129-8B99-4084-8265-242CB6D304A0}"/>
+    <workbookView xWindow="5085" yWindow="3705" windowWidth="21600" windowHeight="11505" xr2:uid="{AFD31129-8B99-4084-8265-242CB6D304A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>firstName</t>
   </si>
@@ -56,12 +56,6 @@
     <t>phone</t>
   </si>
   <si>
-    <t>cv</t>
-  </si>
-  <si>
-    <t>fieldOfStudy</t>
-  </si>
-  <si>
     <t>level</t>
   </si>
   <si>
@@ -86,21 +80,6 @@
     <t>Ghazi</t>
   </si>
   <si>
-    <t>Chiraz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oumaima </t>
-  </si>
-  <si>
-    <t>Ilyes</t>
-  </si>
-  <si>
-    <t>hafsi</t>
-  </si>
-  <si>
-    <t>ben boubaker</t>
-  </si>
-  <si>
     <t>nefzi</t>
   </si>
   <si>
@@ -116,73 +95,31 @@
     <t>ben Ali</t>
   </si>
   <si>
-    <t>ahmed_cv.pdf</t>
-  </si>
-  <si>
-    <t>ali_cv.pdf</t>
-  </si>
-  <si>
-    <t>amine_cv.pdf</t>
-  </si>
-  <si>
-    <t>amira_cv.pdf</t>
-  </si>
-  <si>
-    <t>islem_cv.pdf</t>
-  </si>
-  <si>
-    <t>ghazi_cv.pdf</t>
-  </si>
-  <si>
-    <t>chiraz_cv.pdf</t>
-  </si>
-  <si>
-    <t>oumaima_cv.pdf</t>
-  </si>
-  <si>
-    <t>ilyes_cv.pdf</t>
-  </si>
-  <si>
-    <t>IM</t>
-  </si>
-  <si>
-    <t>CM</t>
-  </si>
-  <si>
-    <t>ING</t>
-  </si>
-  <si>
     <t>active_student</t>
   </si>
   <si>
-    <t>alimeknimekni@gmail.com</t>
-  </si>
-  <si>
-    <t>amineaouidetaouidet@gmail.com</t>
-  </si>
-  <si>
-    <t>amiragafsigafsi@gmail.com</t>
-  </si>
-  <si>
-    <t>islemgafsigafsi@gmail.com</t>
-  </si>
-  <si>
-    <t>ghazinefzinefzi@gmail.com</t>
-  </si>
-  <si>
-    <t>chirazbenboubaker@gmail.com</t>
-  </si>
-  <si>
-    <t>ahmedgafsi88@gmail.com</t>
-  </si>
-  <si>
-    <t>Mzoughi</t>
-  </si>
-  <si>
-    <t>oumaymaamzoughi@gmail.com</t>
-  </si>
-  <si>
-    <t>hafsitsw@gmail.com</t>
+    <t>academicYearlevel</t>
+  </si>
+  <si>
+    <t>1ING</t>
+  </si>
+  <si>
+    <t>aahmedgafsi@gmail.com</t>
+  </si>
+  <si>
+    <t>alimeknimekni123@gmail.com</t>
+  </si>
+  <si>
+    <t>amineaouidet123@gmail.com</t>
+  </si>
+  <si>
+    <t>amiragafsi123@gmail.com</t>
+  </si>
+  <si>
+    <t>islemgafsi123@gmail.com</t>
+  </si>
+  <si>
+    <t>ghazinefzi123@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -624,306 +561,201 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>11526369</v>
+        <v>23456789</v>
       </c>
       <c r="B2" s="2">
         <v>36902</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>25234567</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>11526379</v>
+        <v>23456779</v>
       </c>
       <c r="B3" s="2">
         <v>36903</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>25234568</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>11526389</v>
+        <v>23406789</v>
       </c>
       <c r="B4" s="2">
         <v>36904</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>25234579</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4">
+        <v>21</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
-        <v>38</v>
+      <c r="I4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>11526399</v>
+        <v>23156789</v>
       </c>
       <c r="B5" s="2">
         <v>36905</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>25234581</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5">
+        <v>21</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="J5" t="s">
-        <v>38</v>
+      <c r="I5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>11526319</v>
+        <v>23455789</v>
       </c>
       <c r="B6" s="2">
         <v>36906</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>25234582</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>11526329</v>
+        <v>23477789</v>
       </c>
       <c r="B7" s="2">
         <v>36907</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>25234583</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>11526339</v>
-      </c>
-      <c r="B8" s="2">
-        <v>36908</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8">
-        <v>25234584</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8" t="s">
-        <v>38</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>11526349</v>
-      </c>
-      <c r="B9" s="2">
-        <v>36909</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9">
-        <v>25234585</v>
-      </c>
-      <c r="G9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9" t="s">
-        <v>38</v>
-      </c>
+      <c r="B9" s="2"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>11526359</v>
-      </c>
-      <c r="B10" s="2">
-        <v>36910</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10">
-        <v>25234586</v>
-      </c>
-      <c r="G10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10" t="s">
-        <v>38</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
@@ -958,14 +790,11 @@
     <hyperlink ref="E2" r:id="rId1" xr:uid="{AC674394-A38F-4CF0-BBCF-1EABECDAE26E}"/>
     <hyperlink ref="E3" r:id="rId2" xr:uid="{2683BA0E-D107-49D1-A535-42A8413C1392}"/>
     <hyperlink ref="E4" r:id="rId3" xr:uid="{ED43BC6E-A0FD-4AAD-B36F-16FFC3B24B7E}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{FBC6E1C0-2287-4661-95D5-32E3EFAFC6E3}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{4F197912-C0B7-45BF-9590-4C1BA8176939}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{DF49EFD0-C932-4EE8-BC93-B7A38DD20FA7}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{A5057ADE-532C-464A-8B41-755A876B4057}"/>
-    <hyperlink ref="E9" r:id="rId8" xr:uid="{C76FA67C-0334-4551-B9D8-273D708CFC3B}"/>
-    <hyperlink ref="E10" r:id="rId9" xr:uid="{E0FC9139-189A-467A-A089-323F4CC67101}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{D84D29F8-39EB-4351-86F8-17881FBC6780}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{590CE1DF-607C-4EFA-8235-667ED9937529}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{90B03057-7182-436E-A25D-A1C5B43CD38F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\OneDrive\Bureau\Projects\isamm-student-managment-platform\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DFCFCC-7231-40B0-AB5E-E31B76A902CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20012308-7797-44CF-8881-9015AADA7B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5085" yWindow="3705" windowWidth="21600" windowHeight="11505" xr2:uid="{AFD31129-8B99-4084-8265-242CB6D304A0}"/>
+    <workbookView xWindow="780" yWindow="1230" windowWidth="21600" windowHeight="11505" xr2:uid="{AFD31129-8B99-4084-8265-242CB6D304A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
